--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_7.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_7.xlsx
@@ -517,52 +517,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9987443017965538</v>
+        <v>0.996079645370916</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7717195038195227</v>
+        <v>0.7221132727240454</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9865418551799823</v>
+        <v>0.9870041092816697</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9872372161012297</v>
+        <v>0.9911272015479271</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9870095229536426</v>
+        <v>0.9894603405595053</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008396859668403242</v>
+        <v>0.002327291858326302</v>
       </c>
       <c r="H2" t="n">
-        <v>1.526512729093884</v>
+        <v>0.1649655653925824</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03952405113785151</v>
+        <v>0.008066542861588246</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01295632130916026</v>
+        <v>0.006406333986427779</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02624016140644899</v>
+        <v>0.007236433678040402</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2061569329893105</v>
+        <v>0.02944122892774522</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09163438038423811</v>
+        <v>0.04824201341493017</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000700854811226</v>
+        <v>1.001809394444193</v>
       </c>
       <c r="O2" t="n">
-        <v>0.09553544566651258</v>
+        <v>0.05029577580073852</v>
       </c>
       <c r="P2" t="n">
-        <v>143.5597949840629</v>
+        <v>164.1260999599084</v>
       </c>
       <c r="Q2" t="n">
-        <v>225.2244752502323</v>
+        <v>256.7606626498916</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +572,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9987442860389965</v>
+        <v>0.9961917500664405</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7717194872303321</v>
+        <v>0.7219583547094122</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9865416879741616</v>
+        <v>0.9875668069810334</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9872370510142979</v>
+        <v>0.9912003319087044</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9870093553124411</v>
+        <v>0.9897531340335486</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0083969650392619</v>
+        <v>0.00226074166839231</v>
       </c>
       <c r="H3" t="n">
-        <v>1.526512840025879</v>
+        <v>0.1650575314181785</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03952454219003539</v>
+        <v>0.007717276681346199</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01295648889950335</v>
+        <v>0.006353532435911524</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02624050003390453</v>
+        <v>0.007035404359375997</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2061576719287519</v>
+        <v>0.02905821005894936</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09163495533507887</v>
+        <v>0.04754725721208649</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000700863606141</v>
+        <v>1.001757653815489</v>
       </c>
       <c r="O3" t="n">
-        <v>0.09553604509420094</v>
+        <v>0.04957144238799618</v>
       </c>
       <c r="P3" t="n">
-        <v>143.5597698865379</v>
+        <v>164.1841246953591</v>
       </c>
       <c r="Q3" t="n">
-        <v>225.2244501527074</v>
+        <v>256.8186873853423</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +627,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9987442752963428</v>
+        <v>0.9962874036349474</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7717194620267457</v>
+        <v>0.7218126080987486</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9865415376913267</v>
+        <v>0.9880469966289629</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9872370434592334</v>
+        <v>0.9912635285455008</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9870092364869653</v>
+        <v>0.9900034157593626</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008397036875436076</v>
+        <v>0.002203957578107579</v>
       </c>
       <c r="H4" t="n">
-        <v>1.526513008562377</v>
+        <v>0.1651440529021941</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03952498354257959</v>
+        <v>0.007419223207316049</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01295649656913438</v>
+        <v>0.006307903228359495</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02624074005585698</v>
+        <v>0.006863563217837773</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2061579477242503</v>
+        <v>0.02871988168295327</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09163534730351643</v>
+        <v>0.04694632656670358</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000700869602041</v>
+        <v>1.00171350601464</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09553645374954638</v>
+        <v>0.0489449288809414</v>
       </c>
       <c r="P4" t="n">
-        <v>143.5597527765782</v>
+        <v>164.2350012711186</v>
       </c>
       <c r="Q4" t="n">
-        <v>225.2244330427476</v>
+        <v>256.8695639611018</v>
       </c>
     </row>
     <row r="5">
@@ -682,217 +682,217 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9987442651654321</v>
+        <v>0.9963693139348571</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7717194407354788</v>
+        <v>0.7216764915950049</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9865414026788851</v>
+        <v>0.9884583833047036</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9872370168716864</v>
+        <v>0.9913182159128482</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9870091362659141</v>
+        <v>0.9902181110600063</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00839710462088294</v>
+        <v>0.002155332085740451</v>
       </c>
       <c r="H5" t="n">
-        <v>1.526513150937176</v>
+        <v>0.1652248575387431</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03952538004883761</v>
+        <v>0.0071638757036726</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01295652355986023</v>
+        <v>0.006268417879745088</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0262409424977341</v>
+        <v>0.006716155390016867</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2061580126696079</v>
+        <v>0.02842073732189718</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09163571694968584</v>
+        <v>0.04642555423191468</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000700875256503</v>
+        <v>1.001675701260835</v>
       </c>
       <c r="O5" t="n">
-        <v>0.09553683913231849</v>
+        <v>0.04840198618971318</v>
       </c>
       <c r="P5" t="n">
-        <v>143.5597366410831</v>
+        <v>164.2796209343741</v>
       </c>
       <c r="Q5" t="n">
-        <v>225.2244169072525</v>
+        <v>256.9141836243573</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_6</t>
+          <t>model_23_7_4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9987442378491962</v>
+        <v>0.9964397399593595</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7717194134294537</v>
+        <v>0.72154993569052</v>
       </c>
       <c r="D6" t="n">
-        <v>0.986541130693999</v>
+        <v>0.9888124059489348</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9872366789779072</v>
+        <v>0.9913656055306418</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9870088690668578</v>
+        <v>0.990403077461568</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008397287284678178</v>
+        <v>0.002113524155349932</v>
       </c>
       <c r="H6" t="n">
-        <v>1.526513333532692</v>
+        <v>0.1652999865905758</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03952617881751577</v>
+        <v>0.00694413402566389</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01295686657752828</v>
+        <v>0.006234201649013033</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02624148222744075</v>
+        <v>0.006589159152128592</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2061569406905733</v>
+        <v>0.02815572700476717</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0916367136287535</v>
+        <v>0.04597308076853163</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000700890502774</v>
+        <v>1.001643196941834</v>
       </c>
       <c r="O6" t="n">
-        <v>0.09553787824207748</v>
+        <v>0.04793024999424472</v>
       </c>
       <c r="P6" t="n">
-        <v>143.5596931351804</v>
+        <v>164.3187970178955</v>
       </c>
       <c r="Q6" t="n">
-        <v>225.2243734013498</v>
+        <v>256.9533597078788</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_4</t>
+          <t>model_23_7_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9987442524962367</v>
+        <v>0.9965005090156637</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7717194050020513</v>
+        <v>0.7214331078828436</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9865412822001619</v>
+        <v>0.9891181736769884</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9872368437646262</v>
+        <v>0.9914067918630056</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9870090005774612</v>
+        <v>0.9905629332455225</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008397189339851377</v>
+        <v>0.002077449018441282</v>
       </c>
       <c r="H7" t="n">
-        <v>1.526513389886771</v>
+        <v>0.165369340623911</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03952573387228656</v>
+        <v>0.006754344149964537</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01295669929195056</v>
+        <v>0.006204464311664082</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02624121658211856</v>
+        <v>0.006479403634394007</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2061557616671038</v>
+        <v>0.02792069850379601</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0916361792080583</v>
+        <v>0.04557904143837694</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000700882327682</v>
+        <v>1.001615149685078</v>
       </c>
       <c r="O7" t="n">
-        <v>0.09553732106998687</v>
+        <v>0.04751943559403149</v>
       </c>
       <c r="P7" t="n">
-        <v>143.5597164630468</v>
+        <v>164.3532291427912</v>
       </c>
       <c r="Q7" t="n">
-        <v>225.2243967292162</v>
+        <v>256.9877918327744</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_5</t>
+          <t>model_23_7_6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9987442423088601</v>
+        <v>0.9965531441112911</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7717193839461367</v>
+        <v>0.721325386750856</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9865411312513873</v>
+        <v>0.9893832994383899</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9872368609914013</v>
+        <v>0.9914426859422306</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9870088951739832</v>
+        <v>0.9907016398888274</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008397257462885114</v>
+        <v>0.002046202551959038</v>
       </c>
       <c r="H8" t="n">
-        <v>1.526513530687769</v>
+        <v>0.1654332885411695</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03952617718057077</v>
+        <v>0.006589780722615911</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01295668180394522</v>
+        <v>0.006178548084569255</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02624142949225799</v>
+        <v>0.006384168923002561</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2061577503013678</v>
+        <v>0.02771196420015278</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0916365509111136</v>
+        <v>0.04523497045383183</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000700888013659</v>
+        <v>1.001590856564019</v>
       </c>
       <c r="O8" t="n">
-        <v>0.09553770859721077</v>
+        <v>0.04716071679534916</v>
       </c>
       <c r="P8" t="n">
-        <v>143.5597002379137</v>
+        <v>164.3835392347006</v>
       </c>
       <c r="Q8" t="n">
-        <v>225.2243805040831</v>
+        <v>257.0181019246839</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +902,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9987442298127946</v>
+        <v>0.9965989008315446</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7717193784024143</v>
+        <v>0.7212265688925479</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9865410293515171</v>
+        <v>0.989614034220653</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9872366412822715</v>
+        <v>0.9914740734705839</v>
       </c>
       <c r="F9" t="n">
-        <v>0.987008765888422</v>
+        <v>0.9908224276567773</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008397341024132109</v>
+        <v>0.002019039386229252</v>
       </c>
       <c r="H9" t="n">
-        <v>1.526513567758665</v>
+        <v>0.1654919510905704</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03952647644140755</v>
+        <v>0.006446563758798348</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01295690484478828</v>
+        <v>0.006155885675327556</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02624169064309792</v>
+        <v>0.006301237147377041</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2061545725469401</v>
+        <v>0.02752618003565412</v>
       </c>
       <c r="M9" t="n">
-        <v>0.09163700684839127</v>
+        <v>0.04493372214973129</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000700894988208</v>
+        <v>1.001569738077749</v>
       </c>
       <c r="O9" t="n">
-        <v>0.09553818394468226</v>
+        <v>0.0468466437272731</v>
       </c>
       <c r="P9" t="n">
-        <v>143.5596803359798</v>
+        <v>164.4102668641022</v>
       </c>
       <c r="Q9" t="n">
-        <v>225.2243606021493</v>
+        <v>257.0448295540854</v>
       </c>
     </row>
     <row r="10">
@@ -957,272 +957,272 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9987442327272779</v>
+        <v>0.9966388075998949</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7717193684679624</v>
+        <v>0.7211360206735697</v>
       </c>
       <c r="D10" t="n">
-        <v>0.986541052258077</v>
+        <v>0.9898155493415033</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9872366949815762</v>
+        <v>0.9915015447007482</v>
       </c>
       <c r="F10" t="n">
-        <v>0.987008784550523</v>
+        <v>0.9909279776091053</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008397321534969341</v>
+        <v>0.001995349004653829</v>
       </c>
       <c r="H10" t="n">
-        <v>1.526513634190391</v>
+        <v>0.1655457044248352</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03952640916913075</v>
+        <v>0.006321483424188819</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01295685033117655</v>
+        <v>0.006136050909960022</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02624165294651911</v>
+        <v>0.006228767516450754</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2061540141440702</v>
+        <v>0.0273607465150681</v>
       </c>
       <c r="M10" t="n">
-        <v>0.09163690050939818</v>
+        <v>0.04466932957470739</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000700893361519</v>
+        <v>1.001551319569279</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0955380730786181</v>
+        <v>0.04657099541296236</v>
       </c>
       <c r="P10" t="n">
-        <v>143.5596849777314</v>
+        <v>164.4338726085287</v>
       </c>
       <c r="Q10" t="n">
-        <v>225.2243652439008</v>
+        <v>257.068435298512</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_10</t>
+          <t>model_23_7_9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9987442189541162</v>
+        <v>0.9966737099387993</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7717193593527283</v>
+        <v>0.7210533662103986</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9865409372732775</v>
+        <v>0.989991994950711</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9872364605499663</v>
+        <v>0.9915256825122994</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9870086698096505</v>
+        <v>0.9910204259522231</v>
       </c>
       <c r="G11" t="n">
-        <v>0.008397413636164452</v>
+        <v>0.001974629468577627</v>
       </c>
       <c r="H11" t="n">
-        <v>1.526513695144004</v>
+        <v>0.1655947716846605</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0395267468579544</v>
+        <v>0.006211963722903129</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01295708831775433</v>
+        <v>0.006118622938014759</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02624188471776215</v>
+        <v>0.006165293330458945</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2061529037976236</v>
+        <v>0.02721323707946265</v>
       </c>
       <c r="M11" t="n">
-        <v>0.09163740304135889</v>
+        <v>0.04443680308682913</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000700901048865</v>
+        <v>1.001535210797477</v>
       </c>
       <c r="O11" t="n">
-        <v>0.09553859700440474</v>
+        <v>0.04632856979109894</v>
       </c>
       <c r="P11" t="n">
-        <v>143.5596630420011</v>
+        <v>164.4547490181539</v>
       </c>
       <c r="Q11" t="n">
-        <v>225.2243433081705</v>
+        <v>257.0893117081371</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_9</t>
+          <t>model_23_7_10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9987442269012115</v>
+        <v>0.9967043165267971</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7717193531414452</v>
+        <v>0.7209780222314809</v>
       </c>
       <c r="D12" t="n">
-        <v>0.986541019595121</v>
+        <v>0.9901468637881988</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9872365495909117</v>
+        <v>0.9915469662228291</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9870087326838007</v>
+        <v>0.9911016200621806</v>
       </c>
       <c r="G12" t="n">
-        <v>0.008397360493902667</v>
+        <v>0.001956460075806402</v>
       </c>
       <c r="H12" t="n">
-        <v>1.526513736678882</v>
+        <v>0.1656394991252365</v>
       </c>
       <c r="I12" t="n">
-        <v>0.03952650509411584</v>
+        <v>0.006115836713020103</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01295699792657416</v>
+        <v>0.006103255682817892</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02624175771489344</v>
+        <v>0.006109546197918997</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2061534297934375</v>
+        <v>0.02708150864206027</v>
       </c>
       <c r="M12" t="n">
-        <v>0.09163711308145116</v>
+        <v>0.04423188980595789</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000700896613277</v>
+        <v>1.00152108467994</v>
       </c>
       <c r="O12" t="n">
-        <v>0.09553829470030344</v>
+        <v>0.04611493292763204</v>
       </c>
       <c r="P12" t="n">
-        <v>143.5596756988577</v>
+        <v>164.4732370448954</v>
       </c>
       <c r="Q12" t="n">
-        <v>225.2243559650271</v>
+        <v>257.1077997348787</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_12</t>
+          <t>model_23_7_11</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9987442087600562</v>
+        <v>0.9967312031981564</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7717193326818681</v>
+        <v>0.7209093525815509</v>
       </c>
       <c r="D13" t="n">
-        <v>0.986540810775267</v>
+        <v>0.9902831405495007</v>
       </c>
       <c r="E13" t="n">
-        <v>0.987236406803485</v>
+        <v>0.9915656601703267</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9870085604718234</v>
+        <v>0.9911730480025238</v>
       </c>
       <c r="G13" t="n">
-        <v>0.008397481803890966</v>
+        <v>0.00194049898624375</v>
       </c>
       <c r="H13" t="n">
-        <v>1.526513873492169</v>
+        <v>0.1656802643958093</v>
       </c>
       <c r="I13" t="n">
-        <v>0.03952711835892309</v>
+        <v>0.006031249795516227</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01295714287925799</v>
+        <v>0.006089758287171996</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02624210557510418</v>
+        <v>0.006060504428023939</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2061524644055856</v>
+        <v>0.02696385368613936</v>
       </c>
       <c r="M13" t="n">
-        <v>0.09163777498330569</v>
+        <v>0.04405109517643972</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000700906738573</v>
+        <v>1.001508675447005</v>
       </c>
       <c r="O13" t="n">
-        <v>0.09553898478069026</v>
+        <v>0.0459264414964388</v>
       </c>
       <c r="P13" t="n">
-        <v>143.559646806657</v>
+        <v>164.4896202591511</v>
       </c>
       <c r="Q13" t="n">
-        <v>225.2243270728265</v>
+        <v>257.1241829491344</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_11</t>
+          <t>model_23_7_12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9987442162453367</v>
+        <v>0.9967548619491174</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7717193203070469</v>
+        <v>0.720846937595665</v>
       </c>
       <c r="D14" t="n">
-        <v>0.986540883586673</v>
+        <v>0.9904031892555668</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9872365043391668</v>
+        <v>0.9915821613436282</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9870086339949279</v>
+        <v>0.9912360008029535</v>
       </c>
       <c r="G14" t="n">
-        <v>0.008397431749786103</v>
+        <v>0.00192645412966846</v>
       </c>
       <c r="H14" t="n">
-        <v>1.526513956242655</v>
+        <v>0.1657173166276182</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0395269045254583</v>
+        <v>0.005956735623771633</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01295704386452567</v>
+        <v>0.006077844117374403</v>
       </c>
       <c r="K14" t="n">
-        <v>0.02624195706184143</v>
+        <v>0.006017281611601056</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2061533392326056</v>
+        <v>0.026858730484676</v>
       </c>
       <c r="M14" t="n">
-        <v>0.09163750187442968</v>
+        <v>0.0438913901542029</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000700902560742</v>
+        <v>1.001497756023484</v>
       </c>
       <c r="O14" t="n">
-        <v>0.09553870004500398</v>
+        <v>0.0457599375007704</v>
       </c>
       <c r="P14" t="n">
-        <v>143.5596587279104</v>
+        <v>164.5041484087436</v>
       </c>
       <c r="Q14" t="n">
-        <v>225.2243389940798</v>
+        <v>257.1387110987268</v>
       </c>
     </row>
     <row r="15">
@@ -1232,602 +1232,602 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9987441960009418</v>
+        <v>0.9967757698601207</v>
       </c>
       <c r="C15" t="n">
-        <v>0.771719260293208</v>
+        <v>0.7207903406407126</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9865407135767431</v>
+        <v>0.9905093979137608</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9872361626922623</v>
+        <v>0.9915967794377926</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9870084252888213</v>
+        <v>0.9912916766684844</v>
       </c>
       <c r="G15" t="n">
-        <v>0.008397567124148242</v>
+        <v>0.001914042290522214</v>
       </c>
       <c r="H15" t="n">
-        <v>1.526514357555472</v>
+        <v>0.1657509150249391</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03952740381278622</v>
+        <v>0.005890811962811234</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01295739069223218</v>
+        <v>0.006067289567536764</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0262423786385015</v>
+        <v>0.005979055072057092</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2061536696120728</v>
+        <v>0.02676471252024088</v>
       </c>
       <c r="M15" t="n">
-        <v>0.09163824051207139</v>
+        <v>0.04374976903392993</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000700913859939</v>
+        <v>1.001488106218406</v>
       </c>
       <c r="O15" t="n">
-        <v>0.09553947012797928</v>
+        <v>0.04561228727621126</v>
       </c>
       <c r="P15" t="n">
-        <v>143.5596264863215</v>
+        <v>164.5170757816676</v>
       </c>
       <c r="Q15" t="n">
-        <v>225.224306752491</v>
+        <v>257.1516384716509</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_23</t>
+          <t>model_23_7_14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.998744196761552</v>
+        <v>0.9967942472610233</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7717192511336948</v>
+        <v>0.7207389359760688</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9865406813795328</v>
+        <v>0.9906034055817696</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9872362871502361</v>
+        <v>0.9916096858776443</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9870084239422772</v>
+        <v>0.9913409632881186</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00839756203794364</v>
+        <v>0.001903073307164277</v>
       </c>
       <c r="H16" t="n">
-        <v>1.52651441880518</v>
+        <v>0.1657814310544375</v>
       </c>
       <c r="I16" t="n">
-        <v>0.03952749836996351</v>
+        <v>0.005832461450349498</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01295726434695268</v>
+        <v>0.006057970865583508</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0262423813584581</v>
+        <v>0.005945215330250329</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2061536032484892</v>
+        <v>0.02668050559380765</v>
       </c>
       <c r="M16" t="n">
-        <v>0.09163821276052715</v>
+        <v>0.04362422844205129</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000700913435413</v>
+        <v>1.00147957818722</v>
       </c>
       <c r="O16" t="n">
-        <v>0.09553944119499434</v>
+        <v>0.0454814021614315</v>
       </c>
       <c r="P16" t="n">
-        <v>143.5596276976738</v>
+        <v>164.5285703390321</v>
       </c>
       <c r="Q16" t="n">
-        <v>225.2243079638433</v>
+        <v>257.1631330290154</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_14</t>
+          <t>model_23_7_15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.998744196761552</v>
+        <v>0.9968106073767892</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7717192511336948</v>
+        <v>0.7206924133091881</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9865406813795328</v>
+        <v>0.9906866518120645</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9872362871502361</v>
+        <v>0.9916211970502644</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9870084239422772</v>
+        <v>0.9913846426408603</v>
       </c>
       <c r="G17" t="n">
-        <v>0.00839756203794364</v>
+        <v>0.001893361235725494</v>
       </c>
       <c r="H17" t="n">
-        <v>1.52651441880518</v>
+        <v>0.1658090489191725</v>
       </c>
       <c r="I17" t="n">
-        <v>0.03952749836996351</v>
+        <v>0.005780790556888399</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01295726434695268</v>
+        <v>0.006049659573855417</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0262423813584581</v>
+        <v>0.00591522548655569</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2061536032484892</v>
+        <v>0.02660509813494942</v>
       </c>
       <c r="M17" t="n">
-        <v>0.09163821276052715</v>
+        <v>0.04351277094975099</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000700913435413</v>
+        <v>1.001472027364559</v>
       </c>
       <c r="O17" t="n">
-        <v>0.09553944119499434</v>
+        <v>0.04536519969293517</v>
       </c>
       <c r="P17" t="n">
-        <v>143.5596276976738</v>
+        <v>164.5388031956936</v>
       </c>
       <c r="Q17" t="n">
-        <v>225.2243079638433</v>
+        <v>257.1733658856769</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_15</t>
+          <t>model_23_7_16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.998744196761552</v>
+        <v>0.9968251065642252</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7717192511336948</v>
+        <v>0.7206502175492127</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9865406813795328</v>
+        <v>0.9907605551740105</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9872362871502361</v>
+        <v>0.9916313680144484</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9870084239422772</v>
+        <v>0.9914233966218986</v>
       </c>
       <c r="G18" t="n">
-        <v>0.00839756203794364</v>
+        <v>0.00188475389173115</v>
       </c>
       <c r="H18" t="n">
-        <v>1.52651441880518</v>
+        <v>0.1658340981450558</v>
       </c>
       <c r="I18" t="n">
-        <v>0.03952749836996351</v>
+        <v>0.005734918777133261</v>
       </c>
       <c r="J18" t="n">
-        <v>0.01295726434695268</v>
+        <v>0.006042315938825426</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0262423813584581</v>
+        <v>0.005888617357979344</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2061536032484892</v>
+        <v>0.02653758848989118</v>
       </c>
       <c r="M18" t="n">
-        <v>0.09163821276052715</v>
+        <v>0.04341375233415271</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000700913435413</v>
+        <v>1.001465335431896</v>
       </c>
       <c r="O18" t="n">
-        <v>0.09553944119499434</v>
+        <v>0.04526196564987407</v>
       </c>
       <c r="P18" t="n">
-        <v>143.5596276976738</v>
+        <v>164.5479160560438</v>
       </c>
       <c r="Q18" t="n">
-        <v>225.2243079638433</v>
+        <v>257.182478746027</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_16</t>
+          <t>model_23_7_17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.998744196761552</v>
+        <v>0.9968379848972057</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7717192511336948</v>
+        <v>0.7206120071164275</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9865406813795328</v>
+        <v>0.9908263050161114</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9872362871502361</v>
+        <v>0.9916403704327225</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9870084239422772</v>
+        <v>0.9914578500496337</v>
       </c>
       <c r="G19" t="n">
-        <v>0.00839756203794364</v>
+        <v>0.001877108756958935</v>
       </c>
       <c r="H19" t="n">
-        <v>1.52651441880518</v>
+        <v>0.1658567815085619</v>
       </c>
       <c r="I19" t="n">
-        <v>0.03952749836996351</v>
+        <v>0.005694107883063371</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01295726434695268</v>
+        <v>0.006035816016792824</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0262423813584581</v>
+        <v>0.005864961949928097</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2061536032484892</v>
+        <v>0.02647710845477995</v>
       </c>
       <c r="M19" t="n">
-        <v>0.09163821276052715</v>
+        <v>0.04332561317464457</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000700913435413</v>
+        <v>1.001459391585905</v>
       </c>
       <c r="O19" t="n">
-        <v>0.09553944119499434</v>
+        <v>0.04517007422387245</v>
       </c>
       <c r="P19" t="n">
-        <v>143.5596276976738</v>
+        <v>164.5560451622992</v>
       </c>
       <c r="Q19" t="n">
-        <v>225.2243079638433</v>
+        <v>257.1906078522825</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_17</t>
+          <t>model_23_7_18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.998744196761552</v>
+        <v>0.9968494373358121</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7717192511336948</v>
+        <v>0.7205774760820391</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9865406813795328</v>
+        <v>0.9908848127166953</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9872362871502361</v>
+        <v>0.9916483954609974</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9870084239422772</v>
+        <v>0.9914885153651457</v>
       </c>
       <c r="G20" t="n">
-        <v>0.00839756203794364</v>
+        <v>0.001870310094682547</v>
       </c>
       <c r="H20" t="n">
-        <v>1.52651441880518</v>
+        <v>0.1658772806222378</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03952749836996351</v>
+        <v>0.005657792182606842</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01295726434695268</v>
+        <v>0.006030021789452128</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0262423813584581</v>
+        <v>0.00584390742504789</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2061536032484892</v>
+        <v>0.02642279531829821</v>
       </c>
       <c r="M20" t="n">
-        <v>0.09163821276052715</v>
+        <v>0.04324708192100997</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000700913435413</v>
+        <v>1.00145410584501</v>
       </c>
       <c r="O20" t="n">
-        <v>0.09553944119499434</v>
+        <v>0.04508819973218853</v>
       </c>
       <c r="P20" t="n">
-        <v>143.5596276976738</v>
+        <v>164.5633020716596</v>
       </c>
       <c r="Q20" t="n">
-        <v>225.2243079638433</v>
+        <v>257.1978647616429</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_18</t>
+          <t>model_23_7_19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.998744196761552</v>
+        <v>0.9968596170634066</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7717192511336948</v>
+        <v>0.7205463243141021</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9865406813795328</v>
+        <v>0.9909368908995009</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9872362871502361</v>
+        <v>0.9916555086335218</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9870084239422772</v>
+        <v>0.9915157962632054</v>
       </c>
       <c r="G21" t="n">
-        <v>0.00839756203794364</v>
+        <v>0.001864266968641111</v>
       </c>
       <c r="H21" t="n">
-        <v>1.52651441880518</v>
+        <v>0.1658957736573715</v>
       </c>
       <c r="I21" t="n">
-        <v>0.03952749836996351</v>
+        <v>0.005625467280615899</v>
       </c>
       <c r="J21" t="n">
-        <v>0.01295726434695268</v>
+        <v>0.006024885939794209</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0262423813584581</v>
+        <v>0.005825176610205054</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2061536032484892</v>
+        <v>0.0263741698147635</v>
       </c>
       <c r="M21" t="n">
-        <v>0.09163821276052715</v>
+        <v>0.04317715795002157</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000700913435413</v>
+        <v>1.001449407509197</v>
       </c>
       <c r="O21" t="n">
-        <v>0.09553944119499434</v>
+        <v>0.04501529895299257</v>
       </c>
       <c r="P21" t="n">
-        <v>143.5596276976738</v>
+        <v>164.5697746989087</v>
       </c>
       <c r="Q21" t="n">
-        <v>225.2243079638433</v>
+        <v>257.2043373888919</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_19</t>
+          <t>model_23_7_20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.998744196761552</v>
+        <v>0.996868694951958</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7717192511336948</v>
+        <v>0.7205180986535222</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9865406813795328</v>
+        <v>0.9909833660271433</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9872362871502361</v>
+        <v>0.991661858163875</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9870084239422772</v>
+        <v>0.9915401416775466</v>
       </c>
       <c r="G22" t="n">
-        <v>0.00839756203794364</v>
+        <v>0.001858877941852668</v>
       </c>
       <c r="H22" t="n">
-        <v>1.52651441880518</v>
+        <v>0.1659125296287768</v>
       </c>
       <c r="I22" t="n">
-        <v>0.03952749836996351</v>
+        <v>0.005596620192159141</v>
       </c>
       <c r="J22" t="n">
-        <v>0.01295726434695268</v>
+        <v>0.006020301454716701</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0262423813584581</v>
+        <v>0.005808461271608116</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2061536032484892</v>
+        <v>0.02633045297799368</v>
       </c>
       <c r="M22" t="n">
-        <v>0.09163821276052715</v>
+        <v>0.04311470679307314</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000700913435413</v>
+        <v>1.001445217714481</v>
       </c>
       <c r="O22" t="n">
-        <v>0.09553944119499434</v>
+        <v>0.04495018912100114</v>
       </c>
       <c r="P22" t="n">
-        <v>143.5596276976738</v>
+        <v>164.5755644607165</v>
       </c>
       <c r="Q22" t="n">
-        <v>225.2243079638433</v>
+        <v>257.2101271506997</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_20</t>
+          <t>model_23_7_21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.998744196761552</v>
+        <v>0.9968768284240154</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7717192511336948</v>
+        <v>0.7204926526151981</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9865406813795328</v>
+        <v>0.9910249435893426</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9872362871502361</v>
+        <v>0.9916676300712537</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9870084239422772</v>
+        <v>0.9915619763684957</v>
       </c>
       <c r="G23" t="n">
-        <v>0.00839756203794364</v>
+        <v>0.001854049561491677</v>
       </c>
       <c r="H23" t="n">
-        <v>1.52651441880518</v>
+        <v>0.1659276354963376</v>
       </c>
       <c r="I23" t="n">
-        <v>0.03952749836996351</v>
+        <v>0.005570813020120731</v>
       </c>
       <c r="J23" t="n">
-        <v>0.01295726434695268</v>
+        <v>0.006016134024721958</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0262423813584581</v>
+        <v>0.005793469772705704</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2061536032484892</v>
+        <v>0.02629113380276404</v>
       </c>
       <c r="M23" t="n">
-        <v>0.09163821276052715</v>
+        <v>0.04305867579816728</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000700913435413</v>
+        <v>1.001441463804301</v>
       </c>
       <c r="O23" t="n">
-        <v>0.09553944119499434</v>
+        <v>0.04489177277064198</v>
       </c>
       <c r="P23" t="n">
-        <v>143.5596276976738</v>
+        <v>164.5807661599992</v>
       </c>
       <c r="Q23" t="n">
-        <v>225.2243079638433</v>
+        <v>257.2153288499825</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_21</t>
+          <t>model_23_7_22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.998744196761552</v>
+        <v>0.9968840587718131</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7717192511336948</v>
+        <v>0.720469718832633</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9865406813795328</v>
+        <v>0.9910619596106981</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9872362871502361</v>
+        <v>0.9916727364950039</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9870084239422772</v>
+        <v>0.9915813876849275</v>
       </c>
       <c r="G24" t="n">
-        <v>0.00839756203794364</v>
+        <v>0.001849757314704222</v>
       </c>
       <c r="H24" t="n">
-        <v>1.52651441880518</v>
+        <v>0.1659412499803561</v>
       </c>
       <c r="I24" t="n">
-        <v>0.03952749836996351</v>
+        <v>0.005547837194199971</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01295726434695268</v>
+        <v>0.006012447086920281</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0262423813584581</v>
+        <v>0.005780142140560126</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2061536032484892</v>
+        <v>0.02625599677593168</v>
       </c>
       <c r="M24" t="n">
-        <v>0.09163821276052715</v>
+        <v>0.04300880508342707</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000700913435413</v>
+        <v>1.001438126720702</v>
       </c>
       <c r="O24" t="n">
-        <v>0.09553944119499434</v>
+        <v>0.04483977895632867</v>
       </c>
       <c r="P24" t="n">
-        <v>143.5596276976738</v>
+        <v>164.5854016594758</v>
       </c>
       <c r="Q24" t="n">
-        <v>225.2243079638433</v>
+        <v>257.219964349459</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_22</t>
+          <t>model_23_7_23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.998744196761552</v>
+        <v>0.9968905291683915</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7717192511336948</v>
+        <v>0.7204490444079232</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9865406813795328</v>
+        <v>0.9910951185134945</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9872362871502361</v>
+        <v>0.9916772964543232</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9870084239422772</v>
+        <v>0.9915987736538374</v>
       </c>
       <c r="G25" t="n">
-        <v>0.00839756203794364</v>
+        <v>0.001845916207788718</v>
       </c>
       <c r="H25" t="n">
-        <v>1.52651441880518</v>
+        <v>0.1659535232119524</v>
       </c>
       <c r="I25" t="n">
-        <v>0.03952749836996351</v>
+        <v>0.00552725547983748</v>
       </c>
       <c r="J25" t="n">
-        <v>0.01295726434695268</v>
+        <v>0.006009154707123473</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0262423813584581</v>
+        <v>0.005768205093480477</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2061536032484892</v>
+        <v>0.02622437198017756</v>
       </c>
       <c r="M25" t="n">
-        <v>0.09163821276052715</v>
+        <v>0.04296412698739167</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000700913435413</v>
+        <v>1.001435140383819</v>
       </c>
       <c r="O25" t="n">
-        <v>0.09553944119499434</v>
+        <v>0.04479319882124864</v>
       </c>
       <c r="P25" t="n">
-        <v>143.5596276976738</v>
+        <v>164.5895590703241</v>
       </c>
       <c r="Q25" t="n">
-        <v>225.2243079638433</v>
+        <v>257.2241217603074</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.998744196761552</v>
+        <v>0.9968963181363322</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7717192511336948</v>
+        <v>0.7204304113219648</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9865406813795328</v>
+        <v>0.9911248157785935</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9872362871502361</v>
+        <v>0.9916813651981323</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9870084239422772</v>
+        <v>0.9916143257934886</v>
       </c>
       <c r="G26" t="n">
-        <v>0.00839756203794364</v>
+        <v>0.001842479626348694</v>
       </c>
       <c r="H26" t="n">
-        <v>1.52651441880518</v>
+        <v>0.1659645846166848</v>
       </c>
       <c r="I26" t="n">
-        <v>0.03952749836996351</v>
+        <v>0.005508822402260527</v>
       </c>
       <c r="J26" t="n">
-        <v>0.01295726434695268</v>
+        <v>0.006006216994530625</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0262423813584581</v>
+        <v>0.005757527136780579</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2061536032484892</v>
+        <v>0.02619589169584451</v>
       </c>
       <c r="M26" t="n">
-        <v>0.09163821276052715</v>
+        <v>0.04292411474158429</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000700913435413</v>
+        <v>1.001432468552462</v>
       </c>
       <c r="O26" t="n">
-        <v>0.09553944119499434</v>
+        <v>0.04475148317130048</v>
       </c>
       <c r="P26" t="n">
-        <v>143.5596276976738</v>
+        <v>164.5932859831491</v>
       </c>
       <c r="Q26" t="n">
-        <v>225.2243079638433</v>
+        <v>257.2278486731324</v>
       </c>
     </row>
   </sheetData>

--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_7.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_7.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_0</t>
+          <t>model_23_7_24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.996079645370916</v>
+        <v>0.9999133676733207</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7221132727240454</v>
+        <v>0.7083219715428173</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9870041092816697</v>
+        <v>0.9998944722609441</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9911272015479271</v>
+        <v>0.9990074911038236</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9894603405595053</v>
+        <v>0.9998138661053447</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002327291858326302</v>
+        <v>5.142869143845064e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1649655653925824</v>
+        <v>0.17315267752695</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008066542861588246</v>
+        <v>0.0001653579053927546</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006406333986427779</v>
+        <v>0.0001557505015025609</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007236433678040402</v>
+        <v>0.0001605542034476577</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02944122892774522</v>
+        <v>0.003157718807954865</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04824201341493017</v>
+        <v>0.007171380023290541</v>
       </c>
       <c r="N2" t="n">
-        <v>1.001809394444193</v>
+        <v>1.000039984150775</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05029577580073852</v>
+        <v>0.007476680517685191</v>
       </c>
       <c r="P2" t="n">
-        <v>164.1260999599084</v>
+        <v>171.7506286840934</v>
       </c>
       <c r="Q2" t="n">
-        <v>256.7606626498916</v>
+        <v>264.3851913740767</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_1</t>
+          <t>model_23_7_23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9961917500664405</v>
+        <v>0.9999147954687782</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7219583547094122</v>
+        <v>0.7083199448656129</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9875668069810334</v>
+        <v>0.9998962782513178</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9912003319087044</v>
+        <v>0.9990236929411846</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9897531340335486</v>
+        <v>0.9998169802784964</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00226074166839231</v>
+        <v>5.058109037741383e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1650575314181785</v>
+        <v>0.1731538806500864</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007717276681346199</v>
+        <v>0.0001625279879889194</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006353532435911524</v>
+        <v>0.0001532080111491034</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007035404359375997</v>
+        <v>0.0001578679995690114</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02905821005894936</v>
+        <v>0.003136141638859358</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04754725721208649</v>
+        <v>0.007112038412256632</v>
       </c>
       <c r="N3" t="n">
-        <v>1.001757653815489</v>
+        <v>1.000039325168256</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04957144238799618</v>
+        <v>0.0074148126114155</v>
       </c>
       <c r="P3" t="n">
-        <v>164.1841246953591</v>
+        <v>171.7838655189466</v>
       </c>
       <c r="Q3" t="n">
-        <v>256.8186873853423</v>
+        <v>264.4184282089299</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_2</t>
+          <t>model_23_7_22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9962874036349474</v>
+        <v>0.9999163609565503</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7218126080987486</v>
+        <v>0.7083176507192457</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9880469966289629</v>
+        <v>0.9998982575081748</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9912635285455008</v>
+        <v>0.999041525848545</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9900034157593626</v>
+        <v>0.9998204001990181</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002203957578107579</v>
+        <v>4.965174921024076e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1651440529021941</v>
+        <v>0.173155242554472</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007419223207316049</v>
+        <v>0.0001594265686743877</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006307903228359495</v>
+        <v>0.0001504095634220129</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006863563217837773</v>
+        <v>0.0001549180660482003</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02871988168295327</v>
+        <v>0.003112253472047178</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04694632656670358</v>
+        <v>0.007046399733923754</v>
       </c>
       <c r="N4" t="n">
-        <v>1.00171350601464</v>
+        <v>1.000038602635438</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0489449288809414</v>
+        <v>0.007346379558655196</v>
       </c>
       <c r="P4" t="n">
-        <v>164.2350012711186</v>
+        <v>171.8209538745463</v>
       </c>
       <c r="Q4" t="n">
-        <v>256.8695639611018</v>
+        <v>264.4555165645295</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_3</t>
+          <t>model_23_7_21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9963693139348571</v>
+        <v>0.9999180874320052</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7216764915950049</v>
+        <v>0.7083152260960206</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9884583833047036</v>
+        <v>0.9999004473058574</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9913182159128482</v>
+        <v>0.9990612022664563</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9902181110600063</v>
+        <v>0.9998241794248123</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002155332085740451</v>
+        <v>4.862683880043251e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1652248575387431</v>
+        <v>0.1731566819155567</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0071638757036726</v>
+        <v>0.0001559952399899954</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006268417879745088</v>
+        <v>0.0001473218208644645</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006716155390016867</v>
+        <v>0.0001516582052465341</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02842073732189718</v>
+        <v>0.003085739439079184</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04642555423191468</v>
+        <v>0.006973294687623097</v>
       </c>
       <c r="N5" t="n">
-        <v>1.001675701260835</v>
+        <v>1.000037805800613</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04840198618971318</v>
+        <v>0.007270162279185212</v>
       </c>
       <c r="P5" t="n">
-        <v>164.2796209343741</v>
+        <v>171.862669881587</v>
       </c>
       <c r="Q5" t="n">
-        <v>256.9141836243573</v>
+        <v>264.4972325715702</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_4</t>
+          <t>model_23_7_20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9964397399593595</v>
+        <v>0.9999199807991509</v>
       </c>
       <c r="C6" t="n">
-        <v>0.72154993569052</v>
+        <v>0.7083124451365257</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9888124059489348</v>
+        <v>0.9999028531044213</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9913656055306418</v>
+        <v>0.9990828582645327</v>
       </c>
       <c r="F6" t="n">
-        <v>0.990403077461568</v>
+        <v>0.9998283331080123</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002113524155349932</v>
+        <v>4.750285427353911e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1652999865905758</v>
+        <v>0.173158332813244</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00694413402566389</v>
+        <v>0.0001522254462382604</v>
       </c>
       <c r="J6" t="n">
-        <v>0.006234201649013033</v>
+        <v>0.0001439234306092911</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006589159152128592</v>
+        <v>0.0001480753473324286</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02815572700476717</v>
+        <v>0.003056085041725787</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04597308076853163</v>
+        <v>0.006892231443700879</v>
       </c>
       <c r="N6" t="n">
-        <v>1.001643196941834</v>
+        <v>1.000036931938853</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04793024999424472</v>
+        <v>0.007185648005145177</v>
       </c>
       <c r="P6" t="n">
-        <v>164.3187970178955</v>
+        <v>171.9094415175195</v>
       </c>
       <c r="Q6" t="n">
-        <v>256.9533597078788</v>
+        <v>264.5440042075028</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_5</t>
+          <t>model_23_7_19</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9965005090156637</v>
+        <v>0.999922051157995</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7214331078828436</v>
+        <v>0.7083093293605787</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9891181736769884</v>
+        <v>0.9999054914527311</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9914067918630056</v>
+        <v>0.9991065897506337</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9905629332455225</v>
+        <v>0.9998328892963148</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002077449018441282</v>
+        <v>4.627379982876188e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.165369340623911</v>
+        <v>0.1731601824724407</v>
       </c>
       <c r="I7" t="n">
-        <v>0.006754344149964537</v>
+        <v>0.00014809125598548</v>
       </c>
       <c r="J7" t="n">
-        <v>0.006204464311664082</v>
+        <v>0.0001401993422148464</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006479403634394007</v>
+        <v>0.0001441452991001632</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02792069850379601</v>
+        <v>0.003023184732630553</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04557904143837694</v>
+        <v>0.006802484827528973</v>
       </c>
       <c r="N7" t="n">
-        <v>1.001615149685078</v>
+        <v>1.000035976388618</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04751943559403149</v>
+        <v>0.007092080689721725</v>
       </c>
       <c r="P7" t="n">
-        <v>164.3532291427912</v>
+        <v>171.9618692709404</v>
       </c>
       <c r="Q7" t="n">
-        <v>256.9877918327744</v>
+        <v>264.5964319609236</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_6</t>
+          <t>model_23_7_18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9965531441112911</v>
+        <v>0.9999243116087762</v>
       </c>
       <c r="C8" t="n">
-        <v>0.721325386750856</v>
+        <v>0.7083058444096987</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9893832994383899</v>
+        <v>0.9999083770511787</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9914426859422306</v>
+        <v>0.9991325942715681</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9907016398888274</v>
+        <v>0.9998378742386873</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002046202551959038</v>
+        <v>4.493189859870656e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1654332885411695</v>
+        <v>0.1731622512898251</v>
       </c>
       <c r="I8" t="n">
-        <v>0.006589780722615911</v>
+        <v>0.0001435696342832799</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006178548084569255</v>
+        <v>0.0001361185554405883</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006384168923002561</v>
+        <v>0.0001398454188803858</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02771196420015278</v>
+        <v>0.002986709379232122</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04523497045383183</v>
+        <v>0.006703126031838172</v>
       </c>
       <c r="N8" t="n">
-        <v>1.001590856564019</v>
+        <v>1.000034933103642</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04716071679534916</v>
+        <v>0.006988491984397306</v>
       </c>
       <c r="P8" t="n">
-        <v>164.3835392347006</v>
+        <v>172.0207251579196</v>
       </c>
       <c r="Q8" t="n">
-        <v>257.0181019246839</v>
+        <v>264.6552878479029</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_7</t>
+          <t>model_23_7_17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9965989008315446</v>
+        <v>0.9999267737169427</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7212265688925479</v>
+        <v>0.7083019450038684</v>
       </c>
       <c r="D9" t="n">
-        <v>0.989614034220653</v>
+        <v>0.9999115313327237</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9914740734705839</v>
+        <v>0.9991610074625323</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9908224276567773</v>
+        <v>0.9998433255787694</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002019039386229252</v>
+        <v>4.347028483355307e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1654919510905704</v>
+        <v>0.1731645661455715</v>
       </c>
       <c r="I9" t="n">
-        <v>0.006446563758798348</v>
+        <v>0.0001386269965089213</v>
       </c>
       <c r="J9" t="n">
-        <v>0.006155885675327556</v>
+        <v>0.0001316597855907386</v>
       </c>
       <c r="K9" t="n">
-        <v>0.006301237147377041</v>
+        <v>0.0001351432362594649</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02752618003565412</v>
+        <v>0.002946159351090754</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04493372214973129</v>
+        <v>0.006593199893341098</v>
       </c>
       <c r="N9" t="n">
-        <v>1.001569738077749</v>
+        <v>1.000033796746026</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0468466437272731</v>
+        <v>0.006873886062605934</v>
       </c>
       <c r="P9" t="n">
-        <v>164.4102668641022</v>
+        <v>172.0868659211367</v>
       </c>
       <c r="Q9" t="n">
-        <v>257.0448295540854</v>
+        <v>264.72142861112</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_8</t>
+          <t>model_23_7_16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9966388075998949</v>
+        <v>0.9999294548640489</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7211360206735697</v>
+        <v>0.7082975861402183</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9898155493415033</v>
+        <v>0.9999149780007379</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9915015447007482</v>
+        <v>0.9991920830074374</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9909279776091053</v>
+        <v>0.9998492827792947</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001995349004653829</v>
+        <v>4.187864009175546e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1655457044248352</v>
+        <v>0.1731671537553273</v>
       </c>
       <c r="I10" t="n">
-        <v>0.006321483424188819</v>
+        <v>0.0001332262003911478</v>
       </c>
       <c r="J10" t="n">
-        <v>0.006136050909960022</v>
+        <v>0.0001267832230510209</v>
       </c>
       <c r="K10" t="n">
-        <v>0.006228767516450754</v>
+        <v>0.0001300047117210844</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0273607465150681</v>
+        <v>0.002901037833523805</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04466932957470739</v>
+        <v>0.006471370804687015</v>
       </c>
       <c r="N10" t="n">
-        <v>1.001551319569279</v>
+        <v>1.000032559293516</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04657099541296236</v>
+        <v>0.006746870457426867</v>
       </c>
       <c r="P10" t="n">
-        <v>164.4338726085287</v>
+        <v>172.1614692880654</v>
       </c>
       <c r="Q10" t="n">
-        <v>257.068435298512</v>
+        <v>264.7960319780487</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_9</t>
+          <t>model_23_7_15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9966737099387993</v>
+        <v>0.9999323603365513</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7210533662103986</v>
+        <v>0.7082926201601496</v>
       </c>
       <c r="D11" t="n">
-        <v>0.989991994950711</v>
+        <v>0.999918729572841</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9915256825122994</v>
+        <v>0.9992259032034749</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9910204259522231</v>
+        <v>0.9998557667694778</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001974629468577627</v>
+        <v>4.015382610444136e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1655947716846605</v>
+        <v>0.1731701017756152</v>
       </c>
       <c r="I11" t="n">
-        <v>0.006211963722903129</v>
+        <v>0.0001273476313016714</v>
       </c>
       <c r="J11" t="n">
-        <v>0.006118622938014759</v>
+        <v>0.0001214759532481557</v>
       </c>
       <c r="K11" t="n">
-        <v>0.006165293330458945</v>
+        <v>0.0001244117922749136</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02721323707946265</v>
+        <v>0.002850889456708162</v>
       </c>
       <c r="M11" t="n">
-        <v>0.04443680308682913</v>
+        <v>0.006336704672338878</v>
       </c>
       <c r="N11" t="n">
-        <v>1.001535210797477</v>
+        <v>1.000031218306207</v>
       </c>
       <c r="O11" t="n">
-        <v>0.04632856979109894</v>
+        <v>0.006606471309027345</v>
       </c>
       <c r="P11" t="n">
-        <v>164.4547490181539</v>
+        <v>172.2455856537159</v>
       </c>
       <c r="Q11" t="n">
-        <v>257.0893117081371</v>
+        <v>264.8801483436992</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_10</t>
+          <t>model_23_7_14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9967043165267971</v>
+        <v>0.9999354903602568</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7209780222314809</v>
+        <v>0.7082870337187696</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9901468637881988</v>
+        <v>0.9999227885165669</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9915469662228291</v>
+        <v>0.9992625739617145</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9911016200621806</v>
+        <v>0.9998627892452212</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001956460075806402</v>
+        <v>3.829570882289931e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1656394991252365</v>
+        <v>0.1731734181285401</v>
       </c>
       <c r="I12" t="n">
-        <v>0.006115836713020103</v>
+        <v>0.0001209874227098376</v>
       </c>
       <c r="J12" t="n">
-        <v>0.006103255682817892</v>
+        <v>0.0001157213559762299</v>
       </c>
       <c r="K12" t="n">
-        <v>0.006109546197918997</v>
+        <v>0.0001183543893430338</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02708150864206027</v>
+        <v>0.00279529591612387</v>
       </c>
       <c r="M12" t="n">
-        <v>0.04423188980595789</v>
+        <v>0.00618835267441177</v>
       </c>
       <c r="N12" t="n">
-        <v>1.00152108467994</v>
+        <v>1.000029773679882</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04611493292763204</v>
+        <v>0.006451803659417508</v>
       </c>
       <c r="P12" t="n">
-        <v>164.4732370448954</v>
+        <v>172.3403454184646</v>
       </c>
       <c r="Q12" t="n">
-        <v>257.1077997348787</v>
+        <v>264.9749081084479</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_11</t>
+          <t>model_23_7_13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9967312031981564</v>
+        <v>0.9999388647789217</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7209093525815509</v>
+        <v>0.7082806856494973</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9902831405495007</v>
+        <v>0.99992718839337</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9915656601703267</v>
+        <v>0.9993023643848086</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9911730480025238</v>
+        <v>0.999870405169204</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00194049898624375</v>
+        <v>3.629250813614146e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1656802643958093</v>
+        <v>0.1731771866166825</v>
       </c>
       <c r="I13" t="n">
-        <v>0.006031249795516227</v>
+        <v>0.00011409298510828</v>
       </c>
       <c r="J13" t="n">
-        <v>0.006089758287171996</v>
+        <v>0.0001094772020187407</v>
       </c>
       <c r="K13" t="n">
-        <v>0.006060504428023939</v>
+        <v>0.0001117850935635104</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02696385368613936</v>
+        <v>0.002733328720264012</v>
       </c>
       <c r="M13" t="n">
-        <v>0.04405109517643972</v>
+        <v>0.00602432636368096</v>
       </c>
       <c r="N13" t="n">
-        <v>1.001508675447005</v>
+        <v>1.000028216255882</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0459264414964388</v>
+        <v>0.006280794409057616</v>
       </c>
       <c r="P13" t="n">
-        <v>164.4896202591511</v>
+        <v>172.4477984508568</v>
       </c>
       <c r="Q13" t="n">
-        <v>257.1241829491344</v>
+        <v>265.0823611408401</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9967548619491174</v>
+        <v>0.9999424740373013</v>
       </c>
       <c r="C14" t="n">
-        <v>0.720846937595665</v>
+        <v>0.7082735611536516</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9904031892555668</v>
+        <v>0.9999319285296565</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9915821613436282</v>
+        <v>0.9993452393862439</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9912360008029535</v>
+        <v>0.9998786105768734</v>
       </c>
       <c r="G14" t="n">
-        <v>0.00192645412966846</v>
+        <v>3.414989645017758e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1657173166276182</v>
+        <v>0.1731814160251787</v>
       </c>
       <c r="I14" t="n">
-        <v>0.005956735623771633</v>
+        <v>0.000106665373992742</v>
       </c>
       <c r="J14" t="n">
-        <v>0.006077844117374403</v>
+        <v>0.0001027489973636519</v>
       </c>
       <c r="K14" t="n">
-        <v>0.006017281611601056</v>
+        <v>0.0001047073246554334</v>
       </c>
       <c r="L14" t="n">
-        <v>0.026858730484676</v>
+        <v>0.002664478369606235</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0438913901542029</v>
+        <v>0.00584379127366623</v>
       </c>
       <c r="N14" t="n">
-        <v>1.001497756023484</v>
+        <v>1.000026550444322</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0457599375007704</v>
+        <v>0.006092573566501803</v>
       </c>
       <c r="P14" t="n">
-        <v>164.5041484087436</v>
+        <v>172.5695020083154</v>
       </c>
       <c r="Q14" t="n">
-        <v>257.1387110987268</v>
+        <v>265.2040646982987</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_13</t>
+          <t>model_23_7_11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9967757698601207</v>
+        <v>0.9999463123860136</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7207903406407126</v>
+        <v>0.7082654802936531</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9905093979137608</v>
+        <v>0.9999370092473653</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9915967794377926</v>
+        <v>0.9993912832145428</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9912916766684844</v>
+        <v>0.9998874137514407</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001914042290522214</v>
+        <v>3.187128684651702e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1657509150249391</v>
+        <v>0.1731862131727487</v>
       </c>
       <c r="I15" t="n">
-        <v>0.005890811962811234</v>
+        <v>9.870408489722203e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.006067289567536764</v>
+        <v>9.55235212230557e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.005979055072057092</v>
+        <v>9.71139377385918e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02676471252024088</v>
+        <v>0.002587920444696825</v>
       </c>
       <c r="M15" t="n">
-        <v>0.04374976903392993</v>
+        <v>0.005645466043341065</v>
       </c>
       <c r="N15" t="n">
-        <v>1.001488106218406</v>
+        <v>1.000024778898763</v>
       </c>
       <c r="O15" t="n">
-        <v>0.04561228727621126</v>
+        <v>0.005885805220531871</v>
       </c>
       <c r="P15" t="n">
-        <v>164.5170757816676</v>
+        <v>172.7076101047219</v>
       </c>
       <c r="Q15" t="n">
-        <v>257.1516384716509</v>
+        <v>265.3421727947052</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_14</t>
+          <t>model_23_7_10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9967942472610233</v>
+        <v>0.9999503654034918</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7207389359760688</v>
+        <v>0.7082561900222866</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9906034055817696</v>
+        <v>0.9999424232078936</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9916096858776443</v>
+        <v>0.9994404570947132</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9913409632881186</v>
+        <v>0.9998968046357074</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001903073307164277</v>
+        <v>2.946524059021318e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1657814310544375</v>
+        <v>0.1731917282791507</v>
       </c>
       <c r="I16" t="n">
-        <v>0.005832461450349498</v>
+        <v>9.022061712996383e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.006057970865583508</v>
+        <v>8.780685840333578e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.005945215330250329</v>
+        <v>8.901360788791306e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02668050559380765</v>
+        <v>0.002502816759520598</v>
       </c>
       <c r="M16" t="n">
-        <v>0.04362422844205129</v>
+        <v>0.005428189439418376</v>
       </c>
       <c r="N16" t="n">
-        <v>1.00147957818722</v>
+        <v>1.000022908275311</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0454814021614315</v>
+        <v>0.005659278701755618</v>
       </c>
       <c r="P16" t="n">
-        <v>164.5285703390321</v>
+        <v>172.8645985488393</v>
       </c>
       <c r="Q16" t="n">
-        <v>257.1631330290154</v>
+        <v>265.4991612388226</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_15</t>
+          <t>model_23_7_9</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9968106073767892</v>
+        <v>0.9999546079141097</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7206924133091881</v>
+        <v>0.7082456430343069</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9906866518120645</v>
+        <v>0.9999481605036823</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9916211970502644</v>
+        <v>0.9994926457121089</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9913846426408603</v>
+        <v>0.9999067631264867</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001893361235725494</v>
+        <v>2.694670302044435e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1658090489191725</v>
+        <v>0.1731979894268216</v>
       </c>
       <c r="I17" t="n">
-        <v>0.005780790556888399</v>
+        <v>8.123049545451598e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.006049659573855417</v>
+        <v>7.961710477651667e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00591522548655569</v>
+        <v>8.042367558361367e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02660509813494942</v>
+        <v>0.002408169000509347</v>
       </c>
       <c r="M17" t="n">
-        <v>0.04351277094975099</v>
+        <v>0.005191021385088329</v>
       </c>
       <c r="N17" t="n">
-        <v>1.001472027364559</v>
+        <v>1.000020950193488</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04536519969293517</v>
+        <v>0.005412013912347188</v>
       </c>
       <c r="P17" t="n">
-        <v>164.5388031956936</v>
+        <v>173.0432992099935</v>
       </c>
       <c r="Q17" t="n">
-        <v>257.1733658856769</v>
+        <v>265.6778618999768</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_16</t>
+          <t>model_23_7_8</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9968251065642252</v>
+        <v>0.9999589929819267</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7206502175492127</v>
+        <v>0.7082336861622021</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9907605551740105</v>
+        <v>0.9999541832024058</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9916313680144484</v>
+        <v>0.9995474893172619</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9914233966218986</v>
+        <v>0.99991722222016</v>
       </c>
       <c r="G18" t="n">
-        <v>0.00188475389173115</v>
+        <v>2.434353733927149e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1658340981450558</v>
+        <v>0.1732050875426131</v>
       </c>
       <c r="I18" t="n">
-        <v>0.005734918777133261</v>
+        <v>7.17931583653157e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.006042315938825426</v>
+        <v>7.101071440591844e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.005888617357979344</v>
+        <v>7.140193638561708e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02653758848989118</v>
+        <v>0.002302995163449966</v>
       </c>
       <c r="M18" t="n">
-        <v>0.04341375233415271</v>
+        <v>0.004933917038142362</v>
       </c>
       <c r="N18" t="n">
-        <v>1.001465335431896</v>
+        <v>1.000018926316034</v>
       </c>
       <c r="O18" t="n">
-        <v>0.04526196564987407</v>
+        <v>0.005143964101072361</v>
       </c>
       <c r="P18" t="n">
-        <v>164.5479160560438</v>
+        <v>173.2464883013476</v>
       </c>
       <c r="Q18" t="n">
-        <v>257.182478746027</v>
+        <v>265.8810509913308</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_17</t>
+          <t>model_23_7_7</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9968379848972057</v>
+        <v>0.9999634635107656</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7206120071164275</v>
+        <v>0.7082198207878363</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9908263050161114</v>
+        <v>0.9999604399347084</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9916403704327225</v>
+        <v>0.9996046870261898</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9914578500496337</v>
+        <v>0.9999281081706208</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001877108756958935</v>
+        <v>2.168963830366795e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1658567815085619</v>
+        <v>0.1732133186277896</v>
       </c>
       <c r="I19" t="n">
-        <v>0.005694107883063371</v>
+        <v>6.198909966551662e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.006035816016792824</v>
+        <v>6.203490382666161e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.005864961949928097</v>
+        <v>6.201200174608912e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02647710845477995</v>
+        <v>0.002186067507568231</v>
       </c>
       <c r="M19" t="n">
-        <v>0.04332561317464457</v>
+        <v>0.004657213577201281</v>
       </c>
       <c r="N19" t="n">
-        <v>1.001459391585905</v>
+        <v>1.000016862995031</v>
       </c>
       <c r="O19" t="n">
-        <v>0.04517007422387245</v>
+        <v>0.004855480800943891</v>
       </c>
       <c r="P19" t="n">
-        <v>164.5560451622992</v>
+        <v>173.4773518179659</v>
       </c>
       <c r="Q19" t="n">
-        <v>257.1906078522825</v>
+        <v>266.1119145079491</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_18</t>
+          <t>model_23_7_6</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9968494373358121</v>
+        <v>0.9999679354725425</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7205774760820391</v>
+        <v>0.7082039717138666</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9908848127166953</v>
+        <v>0.9999668615430232</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9916483954609974</v>
+        <v>0.9996635411708705</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9914885153651457</v>
+        <v>0.9999392945547039</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001870310094682547</v>
+        <v>1.903488861427827e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1658772806222378</v>
+        <v>0.1732227273227424</v>
       </c>
       <c r="I20" t="n">
-        <v>0.005657792182606842</v>
+        <v>5.192668660077666e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.006030021789452128</v>
+        <v>5.279915532621895e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00584390742504789</v>
+        <v>5.236292096349781e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02642279531829821</v>
+        <v>0.002055964202740517</v>
       </c>
       <c r="M20" t="n">
-        <v>0.04324708192100997</v>
+        <v>0.004362899106589365</v>
       </c>
       <c r="N20" t="n">
-        <v>1.00145410584501</v>
+        <v>1.000014799012673</v>
       </c>
       <c r="O20" t="n">
-        <v>0.04508819973218853</v>
+        <v>0.004548636754003081</v>
       </c>
       <c r="P20" t="n">
-        <v>164.5633020716596</v>
+        <v>173.7384740395481</v>
       </c>
       <c r="Q20" t="n">
-        <v>257.1978647616429</v>
+        <v>266.3730367295313</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_19</t>
+          <t>model_23_7_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9968596170634066</v>
+        <v>0.9999722819811281</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7205463243141021</v>
+        <v>0.7081855557925683</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9909368908995009</v>
+        <v>0.9999733283781952</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9916555086335218</v>
+        <v>0.9997230187349427</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9915157962632054</v>
+        <v>0.9999505787272347</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001864266968641111</v>
+        <v>1.645461335844291e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1658957736573715</v>
+        <v>0.1732336598091514</v>
       </c>
       <c r="I21" t="n">
-        <v>0.005625467280615899</v>
+        <v>4.179340479122815e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.006024885939794209</v>
+        <v>4.346557608266967e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.005825176610205054</v>
+        <v>4.262949043694892e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0263741698147635</v>
+        <v>0.001911273111351172</v>
       </c>
       <c r="M21" t="n">
-        <v>0.04317715795002157</v>
+        <v>0.004056428645797052</v>
       </c>
       <c r="N21" t="n">
-        <v>1.001449407509197</v>
+        <v>1.000012792931787</v>
       </c>
       <c r="O21" t="n">
-        <v>0.04501529895299257</v>
+        <v>0.004229119211213528</v>
       </c>
       <c r="P21" t="n">
-        <v>164.5697746989087</v>
+        <v>174.0298093454983</v>
       </c>
       <c r="Q21" t="n">
-        <v>257.2043373888919</v>
+        <v>266.6643720354815</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_20</t>
+          <t>model_23_7_4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.996868694951958</v>
+        <v>0.9999763458380597</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7205180986535222</v>
+        <v>0.7081643955373208</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9909833660271433</v>
+        <v>0.9999796940006058</v>
       </c>
       <c r="E22" t="n">
-        <v>0.991661858163875</v>
+        <v>0.999781822385274</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9915401416775466</v>
+        <v>0.9999617095647561</v>
       </c>
       <c r="G22" t="n">
-        <v>0.001858877941852668</v>
+        <v>1.404213233433367e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1659125296287768</v>
+        <v>0.1732462214507417</v>
       </c>
       <c r="I22" t="n">
-        <v>0.005596620192159141</v>
+        <v>3.181871948329355e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.006020301454716701</v>
+        <v>3.423775146108192e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.005808461271608116</v>
+        <v>3.30283226579642e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02633045297799368</v>
+        <v>0.00175033883926889</v>
       </c>
       <c r="M22" t="n">
-        <v>0.04311470679307314</v>
+        <v>0.003747283327203011</v>
       </c>
       <c r="N22" t="n">
-        <v>1.001445217714481</v>
+        <v>1.000010917305511</v>
       </c>
       <c r="O22" t="n">
-        <v>0.04495018912100114</v>
+        <v>0.003906812936387907</v>
       </c>
       <c r="P22" t="n">
-        <v>164.5755644607165</v>
+        <v>174.3468965904675</v>
       </c>
       <c r="Q22" t="n">
-        <v>257.2101271506997</v>
+        <v>266.9814592804508</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_21</t>
+          <t>model_23_7_3</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9968768284240154</v>
+        <v>0.9999799129413615</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7204926526151981</v>
+        <v>0.7081399112362525</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9910249435893426</v>
+        <v>0.9999857538771875</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9916676300712537</v>
+        <v>0.9998380856430883</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9915619763684957</v>
+        <v>0.9999723318098165</v>
       </c>
       <c r="G23" t="n">
-        <v>0.001854049561491677</v>
+        <v>1.192454572355794e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1659276354963376</v>
+        <v>0.1732607563895225</v>
       </c>
       <c r="I23" t="n">
-        <v>0.005570813020120731</v>
+        <v>2.232312612145239e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.006016134024721958</v>
+        <v>2.540858060477731e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.005793469772705704</v>
+        <v>2.386585336311485e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02629113380276404</v>
+        <v>0.00157473530350701</v>
       </c>
       <c r="M23" t="n">
-        <v>0.04305867579816728</v>
+        <v>0.003453193554314316</v>
       </c>
       <c r="N23" t="n">
-        <v>1.001441463804301</v>
+        <v>1.000009270950141</v>
       </c>
       <c r="O23" t="n">
-        <v>0.04489177277064198</v>
+        <v>0.003600203153017585</v>
       </c>
       <c r="P23" t="n">
-        <v>164.5807661599992</v>
+        <v>174.6738232327521</v>
       </c>
       <c r="Q23" t="n">
-        <v>257.2153288499825</v>
+        <v>267.3083859227353</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_22</t>
+          <t>model_23_7_2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9968840587718131</v>
+        <v>0.9999826957146797</v>
       </c>
       <c r="C24" t="n">
-        <v>0.720469718832633</v>
+        <v>0.7081113927856477</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9910619596106981</v>
+        <v>0.9999912264046023</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9916727364950039</v>
+        <v>0.9998892866231061</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9915813876849275</v>
+        <v>0.9999819597413465</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001849757314704222</v>
+        <v>1.027257127231704e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1659412499803561</v>
+        <v>0.1732776861737345</v>
       </c>
       <c r="I24" t="n">
-        <v>0.005547837194199971</v>
+        <v>1.374788629716306e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.006012447086920281</v>
+        <v>1.737381301134941e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.005780142140560126</v>
+        <v>1.556105277581261e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.02625599677593168</v>
+        <v>0.001381141893184399</v>
       </c>
       <c r="M24" t="n">
-        <v>0.04300880508342707</v>
+        <v>0.003205085220757327</v>
       </c>
       <c r="N24" t="n">
-        <v>1.001438126720702</v>
+        <v>1.000007986593225</v>
       </c>
       <c r="O24" t="n">
-        <v>0.04483977895632867</v>
+        <v>0.003341532334046021</v>
       </c>
       <c r="P24" t="n">
-        <v>164.5854016594758</v>
+        <v>174.9720663960925</v>
       </c>
       <c r="Q24" t="n">
-        <v>257.219964349459</v>
+        <v>267.6066290860758</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_23</t>
+          <t>model_23_7_1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9968905291683915</v>
+        <v>0.9999843212289137</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7204490444079232</v>
+        <v>0.7080779544426701</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9910951185134945</v>
+        <v>0.9999957427527211</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9916772964543232</v>
+        <v>0.9999320524906837</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9915987736538374</v>
+        <v>0.9999899522890295</v>
       </c>
       <c r="G25" t="n">
-        <v>0.001845916207788718</v>
+        <v>9.30759580450436e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1659535232119524</v>
+        <v>0.1732975366185873</v>
       </c>
       <c r="I25" t="n">
-        <v>0.00552725547983748</v>
+        <v>6.67094262692446e-06</v>
       </c>
       <c r="J25" t="n">
-        <v>0.006009154707123473</v>
+        <v>1.06627343015586e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.005768205093480477</v>
+        <v>8.666891295276724e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>0.02622437198017756</v>
+        <v>0.001165866841862956</v>
       </c>
       <c r="M25" t="n">
-        <v>0.04296412698739167</v>
+        <v>0.003050835263416293</v>
       </c>
       <c r="N25" t="n">
-        <v>1.001435140383819</v>
+        <v>1.000007236355886</v>
       </c>
       <c r="O25" t="n">
-        <v>0.04479319882124864</v>
+        <v>0.003180715636679548</v>
       </c>
       <c r="P25" t="n">
-        <v>164.5895590703241</v>
+        <v>175.1693594759878</v>
       </c>
       <c r="Q25" t="n">
-        <v>257.2241217603074</v>
+        <v>267.8039221659711</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_23_7_24</t>
+          <t>model_23_7_0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9968963181363322</v>
+        <v>0.9999843064964977</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7204304113219648</v>
+        <v>0.7080386017857285</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9911248157785935</v>
+        <v>0.9999988247758289</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9916813651981323</v>
+        <v>0.9999619431084869</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9916143257934886</v>
+        <v>0.9999954708065103</v>
       </c>
       <c r="G26" t="n">
-        <v>0.001842479626348694</v>
+        <v>9.316341602983503e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1659645846166848</v>
+        <v>0.173320898055694</v>
       </c>
       <c r="I26" t="n">
-        <v>0.005508822402260527</v>
+        <v>1.841531042357661e-06</v>
       </c>
       <c r="J26" t="n">
-        <v>0.006006216994530625</v>
+        <v>5.972117692476947e-06</v>
       </c>
       <c r="K26" t="n">
-        <v>0.005757527136780579</v>
+        <v>3.906763216590682e-06</v>
       </c>
       <c r="L26" t="n">
-        <v>0.02619589169584451</v>
+        <v>0.0009264685489425693</v>
       </c>
       <c r="M26" t="n">
-        <v>0.04292411474158429</v>
+        <v>0.003052268271791243</v>
       </c>
       <c r="N26" t="n">
-        <v>1.001432468552462</v>
+        <v>1.000007243155463</v>
       </c>
       <c r="O26" t="n">
-        <v>0.04475148317130048</v>
+        <v>0.003182209651187757</v>
       </c>
       <c r="P26" t="n">
-        <v>164.5932859831491</v>
+        <v>175.1674810763926</v>
       </c>
       <c r="Q26" t="n">
-        <v>257.2278486731324</v>
+        <v>267.8020437663758</v>
       </c>
     </row>
   </sheetData>
